--- a/people.xlsx
+++ b/people.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t xml:space="preserve">Photo (key)</t>
   </si>
@@ -200,6 +200,150 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.wesquaredance.com/Contact/BoyerDonJolett.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DonSeaman.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don Seaman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.ilsdc.dance/team/don-seaman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuhle.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jim Kuhle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://iowasquaredance.net/merry-rounders-round-dance-club/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TomKathyNickle.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom &amp; Kathy Nickle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://73nsdc.com/about-us/73rd-team-members/tom-and-kathy-nickel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CurtBraffet.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curt Braffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://curtbraffet.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BarryJohnson.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barry Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.ilsdc.dance/team/barry-johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DanPreedy.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dan Preedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancespokane.org/spokane-area-callers-cuers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jesseMillspaugh.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenne Millspaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancene.org/callcuer/millspaugh/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DennisThompson.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dennis Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.facebook.com/dennis.thompson.56/photos/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BobAsp.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bob Asp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.ilsdc.dance/team-2/bob-asp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tannehille.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romney Tannehille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.romneytannehill.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINK-Ladies.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M I N K Ladies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.wesquaredance.com/LynnNelson/MINK/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weaklend.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanny Weaklend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancene.org/callcuer/weaklend/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JerryJunck.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerry Junck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.wesquaredance.com/JerryJunck/JerryJunck.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stairs.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ron &amp; Norma Stairs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancene.org/callcuer/stairs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brianfreed.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Freed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://callerbrian.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sullivan.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenton Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.squaredancemissouri.com/Missouri/History/CallerHallOfFame/SullivanKenton/</t>
   </si>
 </sst>
 </file>
@@ -417,12 +561,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="55.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -647,6 +791,182 @@
       </c>
       <c r="C22" s="1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
